--- a/weryfikacja_LT_LV.xlsx
+++ b/weryfikacja_LT_LV.xlsx
@@ -2307,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3559,60 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teaser.title</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Krok 1 — zapowiedź koszyka 2 (nad przyciskiem Dalej)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W kolejnym kroku: moduły I/O</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kitame žingsnyje: I/O moduliai</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nākamajā solī: I/O moduļi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teaser.note</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Krok 1 — opis pod chipami DI/DO/AI/AO/RTD</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wejścia i wyjścia dwustanowe i analogowe oraz pomiar temperatury RTD — dodasz je opcjonalnie, z rabatem −25%.</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skaitmeniniai ir analoginiai įėjimai bei išėjimai, taip pat temperatūros matavimas RTD — pasirinktinai, su −25% nuolaida.</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diskrētās un analogās ieejas un izejas, kā arī temperatūras mērīšana ar RTD — pievienojiet pēc izvēles ar −25% atlaidi.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
